--- a/ASTquizApp/qBanks/FMX2.xlsx
+++ b/ASTquizApp/qBanks/FMX2.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169CC3D7-9687-405B-8F02-C84E7D4B0566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="92" windowWidth="14799" windowHeight="8003" activeTab="0" tabRatio="600"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -868,192 +874,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="0%"/>
-    <numFmt numFmtId="177" formatCode="@"/>
-    <numFmt numFmtId="178" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="181" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28" x14ac:knownFonts="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <b/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="1"/>
-      <b/>
     </font>
     <font>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF9C0006"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF006100"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF9C6500"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FFFF0000"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="18.0"/>
-      <color rgb="FF1F497D"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="15.0"/>
-      <color rgb="FF1F497D"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="13.0"/>
-      <color rgb="FF1F497D"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF1F497D"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF000000"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FF000000"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Droid Sans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <name val="Calibri"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1066,206 +937,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCE6F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2DCDB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF1DE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4DFEC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAEEF3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDE9D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8CCE4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6B8B7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCC0DA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7DEE8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCD5B4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95B3D7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA9694"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4D79B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1A0C7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92CDDC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFABF8F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4F81BD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0504D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BBB59"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8064A2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BACC6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF79646"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1378,341 +1051,62 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF4F81BD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FFA7BFDE"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF4F81BD"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF4F81BD"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" xfId="0">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="1" applyBorder="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="2" applyBorder="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="4" applyBorder="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="5" applyBorder="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" borderId="6" applyBorder="1" applyAlignment="1" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="2" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" xfId="0">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="3" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="4" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="6" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" applyFont="1" fillId="7" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="9" applyFill="1" borderId="9" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="10" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="13" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" applyFont="1" fillId="0" borderId="14" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" applyFont="1" fillId="0" borderId="15" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" applyFont="1" fillId="0" borderId="16" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" applyFont="1" fillId="0" borderId="17" applyBorder="1" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="12" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="13" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="14" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="15" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="16" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="17" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="18" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="19" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="20" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="21" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="22" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="23" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="24" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="25" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="26" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="27" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="28" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="29" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="30" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="31" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="32" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="33" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="34" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="35" applyFill="1" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1733,37 +1127,356 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr showOutlineSymbols="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O95"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.0" customWidth="1" style="1" hidden="1"/>
-    <col min="2" max="2" width="0.0" customWidth="1" style="1" hidden="1"/>
-    <col min="3" max="3" width="0.0" customWidth="1" style="1" hidden="1"/>
-    <col min="4" max="4" width="0.0" customWidth="1" style="1" hidden="1"/>
-    <col min="5" max="5" width="0.0" customWidth="1" style="1" hidden="1"/>
-    <col min="6" max="6" width="0.0" customWidth="1" style="1" hidden="1"/>
-    <col min="7" max="7" width="11.25" style="1"/>
-    <col min="8" max="8" width="49.125" customWidth="1" style="1"/>
-    <col min="9" max="9" width="15.25" customWidth="1" style="1"/>
-    <col min="10" max="10" width="15.625" customWidth="1" style="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1" style="1"/>
-    <col min="12" max="12" width="13.875" customWidth="1" style="1"/>
-    <col min="13" max="13" width="11.125" customWidth="1" style="1"/>
-    <col min="14" max="14" width="0.0" customWidth="1" style="1" hidden="1"/>
-    <col min="15" max="15" width="0.0" customWidth="1" style="1" hidden="1"/>
+    <col min="1" max="1" width="28" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="1"/>
+    <col min="8" max="8" width="49.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="1" customWidth="1"/>
+    <col min="14" max="15" width="0" style="1" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1810,7 +1523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -1818,7 +1531,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>17</v>
@@ -1827,7 +1540,7 @@
         <v>18</v>
       </c>
       <c r="F2" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>19</v>
@@ -1851,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="N2" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
@@ -1865,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>17</v>
@@ -1874,7 +1587,7 @@
         <v>26</v>
       </c>
       <c r="F3" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>19</v>
@@ -1898,13 +1611,13 @@
         <v>32</v>
       </c>
       <c r="N3" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -1912,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>17</v>
@@ -1921,7 +1634,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>33</v>
@@ -1941,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="N4" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -1955,7 +1668,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>17</v>
@@ -1964,7 +1677,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>19</v>
@@ -1988,13 +1701,13 @@
         <v>26</v>
       </c>
       <c r="N5" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
@@ -2002,7 +1715,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>17</v>
@@ -2011,7 +1724,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>33</v>
@@ -2031,13 +1744,13 @@
         <v>18</v>
       </c>
       <c r="N6" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
@@ -2045,7 +1758,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>40</v>
@@ -2054,7 +1767,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>19</v>
@@ -2078,13 +1791,13 @@
         <v>24</v>
       </c>
       <c r="N7" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>15</v>
       </c>
@@ -2092,7 +1805,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>40</v>
@@ -2101,7 +1814,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>19</v>
@@ -2125,13 +1838,13 @@
         <v>24</v>
       </c>
       <c r="N8" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -2139,7 +1852,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>40</v>
@@ -2148,7 +1861,7 @@
         <v>32</v>
       </c>
       <c r="F9" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>19</v>
@@ -2172,13 +1885,13 @@
         <v>32</v>
       </c>
       <c r="N9" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
@@ -2186,7 +1899,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>40</v>
@@ -2195,7 +1908,7 @@
         <v>32</v>
       </c>
       <c r="F10" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>33</v>
@@ -2215,13 +1928,13 @@
         <v>18</v>
       </c>
       <c r="N10" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -2229,7 +1942,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="5">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>40</v>
@@ -2238,7 +1951,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>19</v>
@@ -2262,13 +1975,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -2276,7 +1989,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="5">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>40</v>
@@ -2285,7 +1998,7 @@
         <v>26</v>
       </c>
       <c r="F12" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>33</v>
@@ -2305,13 +2018,13 @@
         <v>18</v>
       </c>
       <c r="N12" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
@@ -2319,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="5">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>40</v>
@@ -2328,7 +2041,7 @@
         <v>32</v>
       </c>
       <c r="F13" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>19</v>
@@ -2352,13 +2065,13 @@
         <v>18</v>
       </c>
       <c r="N13" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
@@ -2366,7 +2079,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="5">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>40</v>
@@ -2375,7 +2088,7 @@
         <v>32</v>
       </c>
       <c r="F14" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>33</v>
@@ -2395,13 +2108,13 @@
         <v>18</v>
       </c>
       <c r="N14" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -2409,7 +2122,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="5">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>40</v>
@@ -2418,7 +2131,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>33</v>
@@ -2438,13 +2151,13 @@
         <v>18</v>
       </c>
       <c r="N15" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
@@ -2452,7 +2165,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="5">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>67</v>
@@ -2461,7 +2174,7 @@
         <v>18</v>
       </c>
       <c r="F16" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>19</v>
@@ -2485,13 +2198,13 @@
         <v>24</v>
       </c>
       <c r="N16" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>15</v>
       </c>
@@ -2499,7 +2212,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="5">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>67</v>
@@ -2508,7 +2221,7 @@
         <v>32</v>
       </c>
       <c r="F17" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>19</v>
@@ -2532,13 +2245,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>15</v>
       </c>
@@ -2546,7 +2259,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="5">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>67</v>
@@ -2555,7 +2268,7 @@
         <v>26</v>
       </c>
       <c r="F18" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>33</v>
@@ -2575,13 +2288,13 @@
         <v>18</v>
       </c>
       <c r="N18" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O18" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
@@ -2589,7 +2302,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="5">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>67</v>
@@ -2598,7 +2311,7 @@
         <v>32</v>
       </c>
       <c r="F19" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>19</v>
@@ -2622,13 +2335,13 @@
         <v>32</v>
       </c>
       <c r="N19" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>15</v>
       </c>
@@ -2636,7 +2349,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="5">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>67</v>
@@ -2645,7 +2358,7 @@
         <v>32</v>
       </c>
       <c r="F20" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>19</v>
@@ -2669,13 +2382,13 @@
         <v>24</v>
       </c>
       <c r="N20" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>15</v>
       </c>
@@ -2683,7 +2396,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="5">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>67</v>
@@ -2692,7 +2405,7 @@
         <v>18</v>
       </c>
       <c r="F21" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>19</v>
@@ -2716,13 +2429,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>15</v>
       </c>
@@ -2730,7 +2443,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="5">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>67</v>
@@ -2739,7 +2452,7 @@
         <v>26</v>
       </c>
       <c r="F22" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>33</v>
@@ -2759,13 +2472,13 @@
         <v>18</v>
       </c>
       <c r="N22" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
@@ -2773,7 +2486,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="5">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>67</v>
@@ -2782,7 +2495,7 @@
         <v>32</v>
       </c>
       <c r="F23" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>19</v>
@@ -2791,28 +2504,28 @@
         <v>81</v>
       </c>
       <c r="I23" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K23" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N23" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O23" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
@@ -2820,7 +2533,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="5">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>67</v>
@@ -2829,7 +2542,7 @@
         <v>32</v>
       </c>
       <c r="F24" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>33</v>
@@ -2849,13 +2562,13 @@
         <v>18</v>
       </c>
       <c r="N24" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>15</v>
       </c>
@@ -2863,7 +2576,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="5">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>67</v>
@@ -2872,7 +2585,7 @@
         <v>26</v>
       </c>
       <c r="F25" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>19</v>
@@ -2896,13 +2609,13 @@
         <v>18</v>
       </c>
       <c r="N25" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>15</v>
       </c>
@@ -2910,7 +2623,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="5">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>67</v>
@@ -2919,7 +2632,7 @@
         <v>18</v>
       </c>
       <c r="F26" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>19</v>
@@ -2943,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>15</v>
       </c>
@@ -2957,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C27" s="5">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>67</v>
@@ -2966,7 +2679,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>33</v>
@@ -2986,13 +2699,13 @@
         <v>18</v>
       </c>
       <c r="N27" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>15</v>
       </c>
@@ -3000,7 +2713,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="5">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>67</v>
@@ -3009,7 +2722,7 @@
         <v>26</v>
       </c>
       <c r="F28" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>19</v>
@@ -3033,13 +2746,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>15</v>
       </c>
@@ -3047,7 +2760,7 @@
         <v>16</v>
       </c>
       <c r="C29" s="5">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>67</v>
@@ -3056,7 +2769,7 @@
         <v>32</v>
       </c>
       <c r="F29" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>19</v>
@@ -3080,13 +2793,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>15</v>
       </c>
@@ -3094,7 +2807,7 @@
         <v>16</v>
       </c>
       <c r="C30" s="5">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>67</v>
@@ -3103,7 +2816,7 @@
         <v>24</v>
       </c>
       <c r="F30" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>33</v>
@@ -3123,13 +2836,13 @@
         <v>18</v>
       </c>
       <c r="N30" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>15</v>
       </c>
@@ -3137,7 +2850,7 @@
         <v>16</v>
       </c>
       <c r="C31" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>67</v>
@@ -3146,7 +2859,7 @@
         <v>18</v>
       </c>
       <c r="F31" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>33</v>
@@ -3166,13 +2879,13 @@
         <v>18</v>
       </c>
       <c r="N31" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>15</v>
       </c>
@@ -3180,7 +2893,7 @@
         <v>16</v>
       </c>
       <c r="C32" s="5">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>100</v>
@@ -3189,7 +2902,7 @@
         <v>26</v>
       </c>
       <c r="F32" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>19</v>
@@ -3213,13 +2926,13 @@
         <v>18</v>
       </c>
       <c r="N32" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>15</v>
       </c>
@@ -3227,7 +2940,7 @@
         <v>16</v>
       </c>
       <c r="C33" s="5">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>100</v>
@@ -3236,7 +2949,7 @@
         <v>24</v>
       </c>
       <c r="F33" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>33</v>
@@ -3256,13 +2969,13 @@
         <v>18</v>
       </c>
       <c r="N33" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O33" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>15</v>
       </c>
@@ -3270,7 +2983,7 @@
         <v>16</v>
       </c>
       <c r="C34" s="5">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>103</v>
@@ -3279,7 +2992,7 @@
         <v>32</v>
       </c>
       <c r="F34" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>19</v>
@@ -3303,13 +3016,13 @@
         <v>32</v>
       </c>
       <c r="N34" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O34" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>15</v>
       </c>
@@ -3317,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="5">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>103</v>
@@ -3326,7 +3039,7 @@
         <v>24</v>
       </c>
       <c r="F35" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>19</v>
@@ -3350,13 +3063,13 @@
         <v>32</v>
       </c>
       <c r="N35" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O35" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>15</v>
       </c>
@@ -3364,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C36" s="5">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>103</v>
@@ -3373,7 +3086,7 @@
         <v>18</v>
       </c>
       <c r="F36" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>33</v>
@@ -3393,13 +3106,13 @@
         <v>18</v>
       </c>
       <c r="N36" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O36" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>15</v>
       </c>
@@ -3407,7 +3120,7 @@
         <v>16</v>
       </c>
       <c r="C37" s="5">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>103</v>
@@ -3416,7 +3129,7 @@
         <v>26</v>
       </c>
       <c r="F37" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>19</v>
@@ -3440,13 +3153,13 @@
         <v>24</v>
       </c>
       <c r="N37" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O37" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>15</v>
       </c>
@@ -3454,7 +3167,7 @@
         <v>16</v>
       </c>
       <c r="C38" s="5">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>103</v>
@@ -3463,7 +3176,7 @@
         <v>32</v>
       </c>
       <c r="F38" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>19</v>
@@ -3472,28 +3185,28 @@
         <v>119</v>
       </c>
       <c r="I38" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J38" s="5">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="K38" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="L38" s="5">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>32</v>
       </c>
       <c r="N38" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O38" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>15</v>
       </c>
@@ -3501,7 +3214,7 @@
         <v>16</v>
       </c>
       <c r="C39" s="5">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>103</v>
@@ -3510,7 +3223,7 @@
         <v>24</v>
       </c>
       <c r="F39" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>19</v>
@@ -3519,28 +3232,28 @@
         <v>120</v>
       </c>
       <c r="I39" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K39" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>32</v>
       </c>
       <c r="N39" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>15</v>
       </c>
@@ -3548,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="C40" s="5">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>103</v>
@@ -3557,7 +3270,7 @@
         <v>18</v>
       </c>
       <c r="F40" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>33</v>
@@ -3577,13 +3290,13 @@
         <v>18</v>
       </c>
       <c r="N40" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O40" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>15</v>
       </c>
@@ -3591,7 +3304,7 @@
         <v>16</v>
       </c>
       <c r="C41" s="5">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>103</v>
@@ -3600,7 +3313,7 @@
         <v>26</v>
       </c>
       <c r="F41" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>19</v>
@@ -3624,13 +3337,13 @@
         <v>24</v>
       </c>
       <c r="N41" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O41" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>15</v>
       </c>
@@ -3638,7 +3351,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="5">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>127</v>
@@ -3647,7 +3360,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>19</v>
@@ -3671,13 +3384,13 @@
         <v>32</v>
       </c>
       <c r="N42" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>15</v>
       </c>
@@ -3685,7 +3398,7 @@
         <v>16</v>
       </c>
       <c r="C43" s="5">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>127</v>
@@ -3694,7 +3407,7 @@
         <v>32</v>
       </c>
       <c r="F43" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>19</v>
@@ -3703,28 +3416,28 @@
         <v>133</v>
       </c>
       <c r="I43" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K43" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N43" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O43" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>15</v>
       </c>
@@ -3732,7 +3445,7 @@
         <v>16</v>
       </c>
       <c r="C44" s="5">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>127</v>
@@ -3741,7 +3454,7 @@
         <v>18</v>
       </c>
       <c r="F44" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>19</v>
@@ -3750,28 +3463,28 @@
         <v>134</v>
       </c>
       <c r="I44" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="J44" s="5">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="K44" s="5">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="L44" s="5">
-        <v>250.0</v>
+        <v>250</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N44" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O44" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>15</v>
       </c>
@@ -3779,7 +3492,7 @@
         <v>16</v>
       </c>
       <c r="C45" s="5">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>127</v>
@@ -3788,7 +3501,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>19</v>
@@ -3797,28 +3510,28 @@
         <v>135</v>
       </c>
       <c r="I45" s="5">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J45" s="5">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="K45" s="5">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="L45" s="5">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>32</v>
       </c>
       <c r="N45" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O45" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>15</v>
       </c>
@@ -3826,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C46" s="5">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>127</v>
@@ -3835,7 +3548,7 @@
         <v>32</v>
       </c>
       <c r="F46" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>33</v>
@@ -3855,13 +3568,13 @@
         <v>18</v>
       </c>
       <c r="N46" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O46" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>15</v>
       </c>
@@ -3869,7 +3582,7 @@
         <v>16</v>
       </c>
       <c r="C47" s="5">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>127</v>
@@ -3878,7 +3591,7 @@
         <v>26</v>
       </c>
       <c r="F47" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>19</v>
@@ -3887,28 +3600,28 @@
         <v>137</v>
       </c>
       <c r="I47" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K47" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N47" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O47" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>15</v>
       </c>
@@ -3916,7 +3629,7 @@
         <v>16</v>
       </c>
       <c r="C48" s="5">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>127</v>
@@ -3925,7 +3638,7 @@
         <v>24</v>
       </c>
       <c r="F48" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>19</v>
@@ -3934,28 +3647,28 @@
         <v>138</v>
       </c>
       <c r="I48" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K48" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N48" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>15</v>
       </c>
@@ -3963,7 +3676,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="5">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>127</v>
@@ -3972,7 +3685,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>19</v>
@@ -3981,28 +3694,28 @@
         <v>139</v>
       </c>
       <c r="I49" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="J49" s="5">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="K49" s="5">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="L49" s="5">
-        <v>256.0</v>
+        <v>256</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>32</v>
       </c>
       <c r="N49" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O49" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>15</v>
       </c>
@@ -4010,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="C50" s="5">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>127</v>
@@ -4019,7 +3732,7 @@
         <v>26</v>
       </c>
       <c r="F50" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>33</v>
@@ -4039,13 +3752,13 @@
         <v>18</v>
       </c>
       <c r="N50" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O50" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>15</v>
       </c>
@@ -4053,7 +3766,7 @@
         <v>16</v>
       </c>
       <c r="C51" s="5">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>127</v>
@@ -4062,7 +3775,7 @@
         <v>32</v>
       </c>
       <c r="F51" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>19</v>
@@ -4086,13 +3799,13 @@
         <v>24</v>
       </c>
       <c r="N51" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O51" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>15</v>
       </c>
@@ -4100,7 +3813,7 @@
         <v>16</v>
       </c>
       <c r="C52" s="5">
-        <v>51.0</v>
+        <v>51</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>127</v>
@@ -4109,7 +3822,7 @@
         <v>32</v>
       </c>
       <c r="F52" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>19</v>
@@ -4133,13 +3846,13 @@
         <v>32</v>
       </c>
       <c r="N52" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O52" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>15</v>
       </c>
@@ -4147,7 +3860,7 @@
         <v>16</v>
       </c>
       <c r="C53" s="5">
-        <v>52.0</v>
+        <v>52</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>127</v>
@@ -4156,7 +3869,7 @@
         <v>24</v>
       </c>
       <c r="F53" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>19</v>
@@ -4165,28 +3878,28 @@
         <v>151</v>
       </c>
       <c r="I53" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K53" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L53" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M53" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N53" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O53" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>15</v>
       </c>
@@ -4194,7 +3907,7 @@
         <v>16</v>
       </c>
       <c r="C54" s="5">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>127</v>
@@ -4203,7 +3916,7 @@
         <v>18</v>
       </c>
       <c r="F54" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>19</v>
@@ -4227,13 +3940,13 @@
         <v>18</v>
       </c>
       <c r="N54" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O54" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>15</v>
       </c>
@@ -4241,7 +3954,7 @@
         <v>16</v>
       </c>
       <c r="C55" s="5">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>127</v>
@@ -4250,7 +3963,7 @@
         <v>26</v>
       </c>
       <c r="F55" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>19</v>
@@ -4274,13 +3987,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O55" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>15</v>
       </c>
@@ -4288,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="C56" s="5">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>127</v>
@@ -4297,7 +4010,7 @@
         <v>24</v>
       </c>
       <c r="F56" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>19</v>
@@ -4321,13 +4034,13 @@
         <v>32</v>
       </c>
       <c r="N56" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O56" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>15</v>
       </c>
@@ -4335,7 +4048,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="5">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>127</v>
@@ -4344,7 +4057,7 @@
         <v>26</v>
       </c>
       <c r="F57" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>19</v>
@@ -4368,13 +4081,13 @@
         <v>24</v>
       </c>
       <c r="N57" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O57" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="4" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:15" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>15</v>
       </c>
@@ -4382,7 +4095,7 @@
         <v>16</v>
       </c>
       <c r="C58" s="5">
-        <v>57.0</v>
+        <v>57</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>127</v>
@@ -4391,7 +4104,7 @@
         <v>26</v>
       </c>
       <c r="F58" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>33</v>
@@ -4411,13 +4124,13 @@
         <v>18</v>
       </c>
       <c r="N58" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O58" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>15</v>
       </c>
@@ -4425,7 +4138,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="5">
-        <v>58.0</v>
+        <v>58</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>161</v>
@@ -4434,7 +4147,7 @@
         <v>18</v>
       </c>
       <c r="F59" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>19</v>
@@ -4458,13 +4171,13 @@
         <v>32</v>
       </c>
       <c r="N59" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O59" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>15</v>
       </c>
@@ -4472,7 +4185,7 @@
         <v>16</v>
       </c>
       <c r="C60" s="5">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>161</v>
@@ -4481,7 +4194,7 @@
         <v>24</v>
       </c>
       <c r="F60" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>19</v>
@@ -4505,13 +4218,13 @@
         <v>32</v>
       </c>
       <c r="N60" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O60" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>15</v>
       </c>
@@ -4519,7 +4232,7 @@
         <v>16</v>
       </c>
       <c r="C61" s="5">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>161</v>
@@ -4528,7 +4241,7 @@
         <v>32</v>
       </c>
       <c r="F61" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>33</v>
@@ -4548,13 +4261,13 @@
         <v>18</v>
       </c>
       <c r="N61" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O61" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>15</v>
       </c>
@@ -4562,7 +4275,7 @@
         <v>16</v>
       </c>
       <c r="C62" s="5">
-        <v>61.0</v>
+        <v>61</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>161</v>
@@ -4571,7 +4284,7 @@
         <v>26</v>
       </c>
       <c r="F62" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>19</v>
@@ -4580,28 +4293,28 @@
         <v>172</v>
       </c>
       <c r="I62" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K62" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N62" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O62" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>15</v>
       </c>
@@ -4609,7 +4322,7 @@
         <v>16</v>
       </c>
       <c r="C63" s="5">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>161</v>
@@ -4618,7 +4331,7 @@
         <v>32</v>
       </c>
       <c r="F63" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>19</v>
@@ -4627,28 +4340,28 @@
         <v>173</v>
       </c>
       <c r="I63" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K63" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N63" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O63" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>15</v>
       </c>
@@ -4656,7 +4369,7 @@
         <v>16</v>
       </c>
       <c r="C64" s="5">
-        <v>63.0</v>
+        <v>63</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>161</v>
@@ -4665,7 +4378,7 @@
         <v>24</v>
       </c>
       <c r="F64" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>19</v>
@@ -4674,28 +4387,28 @@
         <v>174</v>
       </c>
       <c r="I64" s="5">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J64" s="5">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="K64" s="5">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="L64" s="5">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N64" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O64" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>15</v>
       </c>
@@ -4703,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="C65" s="5">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>161</v>
@@ -4712,7 +4425,7 @@
         <v>26</v>
       </c>
       <c r="F65" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>33</v>
@@ -4732,13 +4445,13 @@
         <v>18</v>
       </c>
       <c r="N65" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O65" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>15</v>
       </c>
@@ -4746,7 +4459,7 @@
         <v>16</v>
       </c>
       <c r="C66" s="5">
-        <v>65.0</v>
+        <v>65</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>161</v>
@@ -4755,7 +4468,7 @@
         <v>26</v>
       </c>
       <c r="F66" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>19</v>
@@ -4764,28 +4477,28 @@
         <v>176</v>
       </c>
       <c r="I66" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K66" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>32</v>
       </c>
       <c r="N66" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O66" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>15</v>
       </c>
@@ -4793,7 +4506,7 @@
         <v>16</v>
       </c>
       <c r="C67" s="5">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>161</v>
@@ -4802,7 +4515,7 @@
         <v>32</v>
       </c>
       <c r="F67" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>33</v>
@@ -4822,13 +4535,13 @@
         <v>18</v>
       </c>
       <c r="N67" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O67" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
         <v>15</v>
       </c>
@@ -4836,7 +4549,7 @@
         <v>16</v>
       </c>
       <c r="C68" s="5">
-        <v>67.0</v>
+        <v>67</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>161</v>
@@ -4845,7 +4558,7 @@
         <v>24</v>
       </c>
       <c r="F68" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>19</v>
@@ -4869,13 +4582,13 @@
         <v>32</v>
       </c>
       <c r="N68" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O68" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
         <v>15</v>
       </c>
@@ -4883,7 +4596,7 @@
         <v>16</v>
       </c>
       <c r="C69" s="5">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>161</v>
@@ -4892,7 +4605,7 @@
         <v>26</v>
       </c>
       <c r="F69" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>19</v>
@@ -4916,13 +4629,13 @@
         <v>24</v>
       </c>
       <c r="N69" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
         <v>15</v>
       </c>
@@ -4930,7 +4643,7 @@
         <v>16</v>
       </c>
       <c r="C70" s="5">
-        <v>69.0</v>
+        <v>69</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>161</v>
@@ -4939,7 +4652,7 @@
         <v>32</v>
       </c>
       <c r="F70" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>19</v>
@@ -4963,13 +4676,13 @@
         <v>18</v>
       </c>
       <c r="N70" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O70" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:15" s="4" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:15" s="4" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
         <v>15</v>
       </c>
@@ -4977,7 +4690,7 @@
         <v>16</v>
       </c>
       <c r="C71" s="5">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>161</v>
@@ -4986,7 +4699,7 @@
         <v>24</v>
       </c>
       <c r="F71" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>33</v>
@@ -5006,13 +4719,13 @@
         <v>18</v>
       </c>
       <c r="N71" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O71" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
         <v>15</v>
       </c>
@@ -5020,7 +4733,7 @@
         <v>16</v>
       </c>
       <c r="C72" s="5">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>187</v>
@@ -5029,7 +4742,7 @@
         <v>18</v>
       </c>
       <c r="F72" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>19</v>
@@ -5053,13 +4766,13 @@
         <v>18</v>
       </c>
       <c r="N72" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O72" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="73" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
         <v>15</v>
       </c>
@@ -5067,7 +4780,7 @@
         <v>16</v>
       </c>
       <c r="C73" s="5">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>194</v>
@@ -5076,7 +4789,7 @@
         <v>24</v>
       </c>
       <c r="F73" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>19</v>
@@ -5100,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O73" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
         <v>15</v>
       </c>
@@ -5114,7 +4827,7 @@
         <v>16</v>
       </c>
       <c r="C74" s="5">
-        <v>73.0</v>
+        <v>73</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>194</v>
@@ -5123,7 +4836,7 @@
         <v>26</v>
       </c>
       <c r="F74" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>19</v>
@@ -5147,13 +4860,13 @@
         <v>32</v>
       </c>
       <c r="N74" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O74" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="75" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
         <v>15</v>
       </c>
@@ -5161,7 +4874,7 @@
         <v>16</v>
       </c>
       <c r="C75" s="5">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>194</v>
@@ -5170,7 +4883,7 @@
         <v>32</v>
       </c>
       <c r="F75" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>19</v>
@@ -5188,19 +4901,19 @@
         <v>0.9</v>
       </c>
       <c r="L75" s="9">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>32</v>
       </c>
       <c r="N75" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O75" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="76" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
         <v>15</v>
       </c>
@@ -5208,7 +4921,7 @@
         <v>16</v>
       </c>
       <c r="C76" s="5">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>194</v>
@@ -5217,7 +4930,7 @@
         <v>18</v>
       </c>
       <c r="F76" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>19</v>
@@ -5241,13 +4954,13 @@
         <v>18</v>
       </c>
       <c r="N76" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O76" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="77" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
         <v>15</v>
       </c>
@@ -5255,7 +4968,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="5">
-        <v>76.0</v>
+        <v>76</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>194</v>
@@ -5264,7 +4977,7 @@
         <v>26</v>
       </c>
       <c r="F77" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>19</v>
@@ -5288,13 +5001,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O77" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="78" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>15</v>
       </c>
@@ -5302,7 +5015,7 @@
         <v>16</v>
       </c>
       <c r="C78" s="5">
-        <v>77.0</v>
+        <v>77</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>194</v>
@@ -5311,7 +5024,7 @@
         <v>32</v>
       </c>
       <c r="F78" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>33</v>
@@ -5331,13 +5044,13 @@
         <v>18</v>
       </c>
       <c r="N78" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O78" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>15</v>
       </c>
@@ -5345,7 +5058,7 @@
         <v>16</v>
       </c>
       <c r="C79" s="5">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>217</v>
@@ -5354,7 +5067,7 @@
         <v>32</v>
       </c>
       <c r="F79" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>19</v>
@@ -5378,13 +5091,13 @@
         <v>32</v>
       </c>
       <c r="N79" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O79" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="80" spans="1:15" s="7" customFormat="1" ht="82.49874" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:15" s="7" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>15</v>
       </c>
@@ -5392,7 +5105,7 @@
         <v>16</v>
       </c>
       <c r="C80" s="5">
-        <v>79.0</v>
+        <v>79</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>217</v>
@@ -5401,7 +5114,7 @@
         <v>18</v>
       </c>
       <c r="F80" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>19</v>
@@ -5425,13 +5138,13 @@
         <v>24</v>
       </c>
       <c r="N80" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O80" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="81" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>15</v>
       </c>
@@ -5439,7 +5152,7 @@
         <v>16</v>
       </c>
       <c r="C81" s="5">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>217</v>
@@ -5448,7 +5161,7 @@
         <v>26</v>
       </c>
       <c r="F81" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>33</v>
@@ -5468,13 +5181,13 @@
         <v>18</v>
       </c>
       <c r="N81" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O81" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="82" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>15</v>
       </c>
@@ -5482,7 +5195,7 @@
         <v>16</v>
       </c>
       <c r="C82" s="5">
-        <v>81.0</v>
+        <v>81</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>217</v>
@@ -5491,7 +5204,7 @@
         <v>32</v>
       </c>
       <c r="F82" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G82" s="5" t="s">
         <v>19</v>
@@ -5515,13 +5228,13 @@
         <v>24</v>
       </c>
       <c r="N82" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O82" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>15</v>
       </c>
@@ -5529,7 +5242,7 @@
         <v>16</v>
       </c>
       <c r="C83" s="5">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>217</v>
@@ -5538,7 +5251,7 @@
         <v>24</v>
       </c>
       <c r="F83" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>19</v>
@@ -5547,28 +5260,28 @@
         <v>233</v>
       </c>
       <c r="I83" s="5">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="J83" s="5">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K83" s="5">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="L83" s="5">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="M83" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N83" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O83" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="84" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>15</v>
       </c>
@@ -5576,7 +5289,7 @@
         <v>16</v>
       </c>
       <c r="C84" s="5">
-        <v>83.0</v>
+        <v>83</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>234</v>
@@ -5585,7 +5298,7 @@
         <v>18</v>
       </c>
       <c r="F84" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G84" s="5" t="s">
         <v>19</v>
@@ -5609,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O84" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="85" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>15</v>
       </c>
@@ -5623,7 +5336,7 @@
         <v>16</v>
       </c>
       <c r="C85" s="5">
-        <v>84.0</v>
+        <v>84</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>234</v>
@@ -5632,7 +5345,7 @@
         <v>26</v>
       </c>
       <c r="F85" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>33</v>
@@ -5652,13 +5365,13 @@
         <v>18</v>
       </c>
       <c r="N85" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O85" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="86" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>15</v>
       </c>
@@ -5666,7 +5379,7 @@
         <v>16</v>
       </c>
       <c r="C86" s="5">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>234</v>
@@ -5675,7 +5388,7 @@
         <v>32</v>
       </c>
       <c r="F86" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G86" s="5" t="s">
         <v>19</v>
@@ -5699,13 +5412,13 @@
         <v>32</v>
       </c>
       <c r="N86" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O86" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>15</v>
       </c>
@@ -5713,7 +5426,7 @@
         <v>16</v>
       </c>
       <c r="C87" s="5">
-        <v>86.0</v>
+        <v>86</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>234</v>
@@ -5722,7 +5435,7 @@
         <v>32</v>
       </c>
       <c r="F87" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>19</v>
@@ -5746,13 +5459,13 @@
         <v>32</v>
       </c>
       <c r="N87" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O87" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="88" spans="1:15" s="7" customFormat="1" ht="65.99899" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:15" s="7" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>15</v>
       </c>
@@ -5760,7 +5473,7 @@
         <v>16</v>
       </c>
       <c r="C88" s="5">
-        <v>87.0</v>
+        <v>87</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>250</v>
@@ -5769,7 +5482,7 @@
         <v>24</v>
       </c>
       <c r="F88" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>33</v>
@@ -5789,13 +5502,13 @@
         <v>18</v>
       </c>
       <c r="N88" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O88" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="89" spans="1:15" s="7" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:15" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>15</v>
       </c>
@@ -5803,7 +5516,7 @@
         <v>16</v>
       </c>
       <c r="C89" s="5">
-        <v>88.0</v>
+        <v>88</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>250</v>
@@ -5812,7 +5525,7 @@
         <v>18</v>
       </c>
       <c r="F89" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G89" s="5" t="s">
         <v>19</v>
@@ -5836,13 +5549,13 @@
         <v>32</v>
       </c>
       <c r="N89" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O89" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:15" s="10" customFormat="1" ht="32.999496" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:15" s="10" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>257</v>
       </c>
@@ -5850,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C90" s="5">
-        <v>89.0</v>
+        <v>89</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>187</v>
@@ -5859,7 +5572,7 @@
         <v>26</v>
       </c>
       <c r="F90" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="5" t="s">
         <v>33</v>
@@ -5879,13 +5592,13 @@
         <v>18</v>
       </c>
       <c r="N90" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O90" s="12" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="91" spans="1:15" s="10" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:15" s="10" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>257</v>
       </c>
@@ -5893,7 +5606,7 @@
         <v>16</v>
       </c>
       <c r="C91" s="5">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>194</v>
@@ -5902,7 +5615,7 @@
         <v>32</v>
       </c>
       <c r="F91" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G91" s="5" t="s">
         <v>19</v>
@@ -5926,13 +5639,13 @@
         <v>18</v>
       </c>
       <c r="N91" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O91" s="12" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="92" spans="1:15" s="10" customFormat="1" ht="32.999496" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:15" s="10" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>257</v>
       </c>
@@ -5940,7 +5653,7 @@
         <v>16</v>
       </c>
       <c r="C92" s="5">
-        <v>91.0</v>
+        <v>91</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>194</v>
@@ -5949,7 +5662,7 @@
         <v>26</v>
       </c>
       <c r="F92" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>19</v>
@@ -5973,13 +5686,13 @@
         <v>24</v>
       </c>
       <c r="N92" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O92" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="93" spans="1:15" s="10" customFormat="1" ht="32.999496" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:15" s="10" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>257</v>
       </c>
@@ -5987,7 +5700,7 @@
         <v>16</v>
       </c>
       <c r="C93" s="5">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>194</v>
@@ -5996,7 +5709,7 @@
         <v>24</v>
       </c>
       <c r="F93" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>19</v>
@@ -6020,13 +5733,13 @@
         <v>18</v>
       </c>
       <c r="N93" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O93" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="10" customFormat="1" ht="32.999496" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:15" s="10" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>257</v>
       </c>
@@ -6034,7 +5747,7 @@
         <v>16</v>
       </c>
       <c r="C94" s="5">
-        <v>93.0</v>
+        <v>93</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>194</v>
@@ -6043,7 +5756,7 @@
         <v>26</v>
       </c>
       <c r="F94" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>19</v>
@@ -6067,13 +5780,13 @@
         <v>18</v>
       </c>
       <c r="N94" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O94" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="95" spans="1:15" s="10" customFormat="1" ht="49.499245" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:15" s="10" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>257</v>
       </c>
@@ -6081,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C95" s="5">
-        <v>94.0</v>
+        <v>94</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>277</v>
@@ -6090,7 +5803,7 @@
         <v>24</v>
       </c>
       <c r="F95" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>19</v>
@@ -6114,7 +5827,7 @@
         <v>18</v>
       </c>
       <c r="N95" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O95" s="5" t="s">
         <v>193</v>
@@ -6123,42 +5836,14 @@
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <conditionalFormatting sqref="H2:H71">
-    <cfRule type="duplicateValues" priority="7" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="1" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="3" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <pageMargins left="0.6999125161508876" right="0.6999125161508876" top="0.7499062639521802" bottom="0.7499062639521802" header="0.2999625102741512" footer="0.2999625102741512"/>
-  <pageSetup paperSize="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr showOutlineSymbols="1"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="11.25" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="0" type="noConversion"/>
-  <pageMargins left="0.6999125161508876" right="0.6999125161508876" top="0.7499062639521802" bottom="0.7499062639521802" header="0.2999625102741512" footer="0.2999625102741512"/>
-  <pageSetup paperSize="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr showOutlineSymbols="1"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="11.25" x14ac:dyDescent="0.15"/>
-  <sheetData/>
-  <phoneticPr fontId="0" type="noConversion"/>
-  <pageMargins left="0.6999125161508876" right="0.6999125161508876" top="0.7499062639521802" bottom="0.7499062639521802" header="0.2999625102741512" footer="0.2999625102741512"/>
+  <pageMargins left="0.69991251615088756" right="0.69991251615088756" top="0.74990626395218019" bottom="0.74990626395218019" header="0.29996251027415122" footer="0.29996251027415122"/>
   <pageSetup paperSize="0"/>
 </worksheet>
 </file>